--- a/astro-site/public/dl/pastry-shop-checklist-templates/06-pastry-shop-holiday-event-checklists.xlsx
+++ b/astro-site/public/dl/pastry-shop-checklist-templates/06-pastry-shop-holiday-event-checklists.xlsx
@@ -879,7 +879,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Hire seasonal help if needed (under 18: no dough mixers, industrial mixers, sheeters or dividers, and no cleaning them — 29 CFR 570.62, benchtop mixers of 5 qt or less excepted; ages 14–15: no baking — 29 CFR 570.33(h))</t>
+          <t>Hire seasonal help if needed. Ages 16–17: no dough or batter mixers, sheeters, dividers or rounders, and no cleaning them (29 CFR 570.62, HO 11), except portable countertop mixers of 5 qt or less and ½ hp or less; ages 14–15: no power-driven machinery and no baking (29 CFR 570.33(e) and (h)), and no work before 7 AM or after 7 PM during the school year (29 CFR 570.35)</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Set and post shop hours for Dec 24, 25 and 31 and Jan 6</t>
+          <t>Set and post shop hours for Dec 24, 25 and 31 and Jan 1 (and Jan 6 if you sell roscas)</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Close the rosca de Reyes orders (and King cake if you make it) and assign pickup slots → 11 Cake Orders · sheet "Order Form"</t>
+          <t>Close the rosca de Reyes orders and assign pickup slots (King cakes sell from Jan 6 until Mardi Gras) → 11 Cake Orders · sheet "Order Form"</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Bake the first batch of roscas overnight Jan 4 into Jan 5 (60–70% of volume, for the afternoon sale on the 5th)</t>
+          <t>Bake the first batch of roscas overnight Jan 4 into Jan 5 (about a third of the volume, for pickups on Jan 5 and the morning of Jan 6)</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Bake the second batch overnight Jan 5 into Jan 6 and fill to order</t>
+          <t>Bake the main batch overnight Jan 5 into Jan 6 (60–70% of the volume: Jan 6 is the big day, when families cut the rosca in the afternoon or evening)</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Fill with whipped cream, pastry cream or cream cheese</t>
+          <t>If you sell filled roscas (whipped cream, pastry cream or cream cheese), fill to order and keep them in the refrigerated case at 41 °F or below; most Mexican-style roscas are sold unfilled</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Counter associate</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Make chocolate figures (bunnies, eggs, bells)</t>
+          <t>Make chocolate figures (bunnies, eggs, chicks)</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Counter associate</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Bake the fruit pies (apple, pecan)</t>
+          <t>Bake the fruit pies (apple, cherry) and the nut pies (pecan; it is egg-based: hold it cold unless your health department accepts it as non-TCS)</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Bake the cream pies (pumpkin, sweet potato), cool them and hold at 41 °F or below: they are TCS foods (FDA Food Code 3-501.16)</t>
+          <t>Bake the custard pies (pumpkin, sweet potato), cool them from 135 °F to 70 °F within 2 h and to 41 °F within 4 more h (FDA Food Code 3-501.14), and hold at 41 °F or below: they are TCS foods (3-501.16)</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Restock the case every 2 h: cream pies come out of the refrigerated case</t>
+          <t>Restock the case every 2 h: custard pies come out of the refrigerated case</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
